--- a/data/trans_orig/IP05A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73586</t>
+          <t>73280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86854</t>
+          <t>86765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78056</t>
+          <t>78455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89496</t>
+          <t>88909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155254</t>
+          <t>155485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172668</t>
+          <t>173343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23013</t>
+          <t>22352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>38539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,82 +974,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5732</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>6273</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2915</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>11390</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5684</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>6273</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>12032</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72721</t>
+          <t>72292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60049</t>
+          <t>60089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72509</t>
+          <t>72153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124481</t>
+          <t>123266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141421</t>
+          <t>141762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39449</t>
+          <t>39258</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58754</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77805</t>
+          <t>77674</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89195</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129193</t>
+          <t>129059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144874</t>
+          <t>144931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>33104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>140635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158798</t>
+          <t>160407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148944</t>
+          <t>148124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167400</t>
+          <t>166383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294105</t>
+          <t>295389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321406</t>
+          <t>321548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>33239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>51610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26901</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>44699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65363</t>
+          <t>65173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91083</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23635</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63031</t>
+          <t>63126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78636</t>
+          <t>77957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80344</t>
+          <t>81382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97513</t>
+          <t>97811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148950</t>
+          <t>149320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>171946</t>
+          <t>171258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>32916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66048</t>
+          <t>66014</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47028</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59455</t>
+          <t>59125</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55144</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>92555</t>
+          <t>92861</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110321</t>
+          <t>111137</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25915</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>458134</t>
+          <t>457421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>495693</t>
+          <t>495408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>512528</t>
+          <t>513076</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>549158</t>
+          <t>549176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>981353</t>
+          <t>983384</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1029887</t>
+          <t>1031676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>113688</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>148416</t>
+          <t>148667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106235</t>
+          <t>105331</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>139809</t>
+          <t>137835</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230381</t>
+          <t>229974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>276714</t>
+          <t>276222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39653</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49678</t>
+          <t>50391</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>73801</t>
+          <t>75247</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65756</t>
+          <t>64756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77941</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70200</t>
+          <t>69833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81348</t>
+          <t>81164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139498</t>
+          <t>139607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155206</t>
+          <t>156258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68951</t>
+          <t>68489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>81312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77384</t>
+          <t>76769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88518</t>
+          <t>88567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150681</t>
+          <t>150224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167722</t>
+          <t>166930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>34321</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76222</t>
+          <t>76444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73955</t>
+          <t>73689</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82477</t>
+          <t>82443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141931</t>
+          <t>141535</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156858</t>
+          <t>155869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168423</t>
+          <t>167841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184737</t>
+          <t>184059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>178055</t>
+          <t>179282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197177</t>
+          <t>197929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352542</t>
+          <t>352486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377741</t>
+          <t>377298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31652</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24370</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42712</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44879</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68097</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119415</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133742</t>
+          <t>133689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,82 +5998,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>116219</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>108255</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>123331</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>82,39%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>76,75%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>243062</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>232320</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>253422</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>83,75%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>80,05%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>116219</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>108027</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>123292</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>82,39%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>76,58%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>243062</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>232203</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>253294</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>80,01%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>27052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26691</t>
+          <t>26885</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48646</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>36972</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>47459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55558</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66171</t>
+          <t>65906</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>96893</t>
+          <t>96571</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>111203</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25134</t>
+          <t>24727</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>548797</t>
+          <t>548791</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>581668</t>
+          <t>580118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>588826</t>
+          <t>588405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>619911</t>
+          <t>621398</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1145816</t>
+          <t>1148069</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1190565</t>
+          <t>1191935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>74685</t>
+          <t>75469</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105083</t>
+          <t>103932</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74930</t>
+          <t>74999</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104534</t>
+          <t>103885</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>158882</t>
+          <t>160133</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>198603</t>
+          <t>199641</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30413</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59810</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65575</t>
+          <t>64848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>75710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86459</t>
+          <t>86998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95734</t>
+          <t>95675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>155972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169136</t>
+          <t>169263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84708</t>
+          <t>83432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96280</t>
+          <t>95985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93342</t>
+          <t>92471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103918</t>
+          <t>103734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182417</t>
+          <t>182089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197503</t>
+          <t>197801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33404</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>55113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60618</t>
+          <t>60592</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62826</t>
+          <t>63679</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72112</t>
+          <t>72170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121274</t>
+          <t>120949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131689</t>
+          <t>131342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183665</t>
+          <t>183139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200154</t>
+          <t>199863</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177967</t>
+          <t>178523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193590</t>
+          <t>193265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>366138</t>
+          <t>367146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388039</t>
+          <t>388954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26179</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49895</t>
+          <t>50580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113491</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125516</t>
+          <t>125572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110564</t>
+          <t>110104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125253</t>
+          <t>126317</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>227049</t>
+          <t>227817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>247840</t>
+          <t>247946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>43788</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>53739</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64387</t>
+          <t>63930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102700</t>
+          <t>102144</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115516</t>
+          <t>115872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -10091,82 +10091,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5922</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>568276</t>
+          <t>569604</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>597039</t>
+          <t>597074</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>609741</t>
+          <t>609460</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>637893</t>
+          <t>639287</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1189465</t>
+          <t>1187609</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1227611</t>
+          <t>1228352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>53771</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>78335</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58124</t>
+          <t>57129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83207</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117234</t>
+          <t>118480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>152043</t>
+          <t>153528</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29477</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23024</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>46962</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93200</t>
+          <t>92417</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101205</t>
+          <t>101379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109705</t>
+          <t>110650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>128047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207035</t>
+          <t>206965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227002</t>
+          <t>227414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29811</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77077</t>
+          <t>77711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87968</t>
+          <t>88279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84188</t>
+          <t>84317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92780</t>
+          <t>92791</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164617</t>
+          <t>165158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179111</t>
+          <t>179035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41737</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>52829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62372</t>
+          <t>62419</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98760</t>
+          <t>98298</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110439</t>
+          <t>110220</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118066</t>
+          <t>114048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202988</t>
+          <t>203133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183817</t>
+          <t>184065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201851</t>
+          <t>202293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>286255</t>
+          <t>297232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>398985</t>
+          <t>399081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97012</t>
+          <t>99037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136363</t>
+          <t>128391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99707</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110633</t>
+          <t>110567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138982</t>
+          <t>136208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>152969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242241</t>
+          <t>242080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>260349</t>
+          <t>260609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27866</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60850</t>
+          <t>61011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68070</t>
+          <t>68106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>59402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>124302</t>
+          <t>124285</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134711</t>
+          <t>135049</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475894</t>
+          <t>490366</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>601905</t>
+          <t>603169</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>658811</t>
+          <t>658305</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>691110</t>
+          <t>690871</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1152713</t>
+          <t>1147502</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1282810</t>
+          <t>1282970</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>152680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>67443</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>84069</t>
+          <t>84995</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>217104</t>
+          <t>225911</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22079</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31876</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27661</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48384</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
